--- a/scripts/test_report/2025-12-29-10-53-12_450_joint_movement_times(插补).xlsx
+++ b/scripts/test_report/2025-12-29-10-53-12_450_joint_movement_times(插补).xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,6 +677,1176 @@
         <v>4.706</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>j1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.604</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4.581</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>j2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.659</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.749</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>j3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4.393</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>j4</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4.577</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>j5</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2.656</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4.589</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>j6</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3.098</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4.663</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>j1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2.566</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4.64</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>j2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.691</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>j3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3.438</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4.44</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>j4</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4.587</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>j5</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4.591</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>j6</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>3.074</v>
+      </c>
+      <c r="C31" t="n">
+        <v>4.661</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>j1</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3.422</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4.593</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>j2</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2.628</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3.707</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>j3</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2.203</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>j4</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2.881</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4.568</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>j5</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2.643</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4.589</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>j6</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3.076</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>j1</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4.589</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>j2</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2.699</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3.766</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>j3</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4.397</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>j4</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2.864</v>
+      </c>
+      <c r="C41" t="n">
+        <v>4.595</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>j5</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2.671</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4.625</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>j6</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4.656</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>j1</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2.572</v>
+      </c>
+      <c r="C44" t="n">
+        <v>4.584</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>j2</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2.656</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3.695</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>j3</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2.259</v>
+      </c>
+      <c r="C46" t="n">
+        <v>4.419</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>j4</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2.906</v>
+      </c>
+      <c r="C47" t="n">
+        <v>4.621</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>j5</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2.659</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4.579</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>j6</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4.672</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>j1</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2.566</v>
+      </c>
+      <c r="C50" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>j2</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2.647</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3.696</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>j3</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="C52" t="n">
+        <v>4.424</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>j4</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C53" t="n">
+        <v>4.574</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>j5</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2.712</v>
+      </c>
+      <c r="C54" t="n">
+        <v>4.584</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>j6</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3.104</v>
+      </c>
+      <c r="C55" t="n">
+        <v>4.646</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>j1</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2.584</v>
+      </c>
+      <c r="C56" t="n">
+        <v>4.578</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>j2</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2.674</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3.732</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>j3</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2.217</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4.398</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>j4</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2.889</v>
+      </c>
+      <c r="C59" t="n">
+        <v>4.594</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>j5</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2.654</v>
+      </c>
+      <c r="C60" t="n">
+        <v>4.605</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>j6</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3.087</v>
+      </c>
+      <c r="C61" t="n">
+        <v>4.664</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>j1</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2.612</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4.581</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>j2</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2.652</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>j3</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="C64" t="n">
+        <v>4.382</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>j4</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2.904</v>
+      </c>
+      <c r="C65" t="n">
+        <v>4.58</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>j5</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2.693</v>
+      </c>
+      <c r="C66" t="n">
+        <v>4.591</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>j6</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C67" t="n">
+        <v>4.651</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>j1</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="C68" t="n">
+        <v>4.579</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>j2</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2.692</v>
+      </c>
+      <c r="C69" t="n">
+        <v>3.693</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>j3</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2.226</v>
+      </c>
+      <c r="C70" t="n">
+        <v>4.424</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>j4</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="C71" t="n">
+        <v>4.574</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>j5</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="C72" t="n">
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>j6</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>3.037</v>
+      </c>
+      <c r="C73" t="n">
+        <v>4.689</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>j1</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2.573</v>
+      </c>
+      <c r="C74" t="n">
+        <v>4.601</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>j2</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>2.639</v>
+      </c>
+      <c r="C75" t="n">
+        <v>3.705</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>j3</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2.239</v>
+      </c>
+      <c r="C76" t="n">
+        <v>4.408</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>j4</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2.879</v>
+      </c>
+      <c r="C77" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>j5</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2.648</v>
+      </c>
+      <c r="C78" t="n">
+        <v>4.583</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>j6</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>3.051</v>
+      </c>
+      <c r="C79" t="n">
+        <v>4.644</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>j1</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="C80" t="n">
+        <v>4.588</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>j2</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>2.647</v>
+      </c>
+      <c r="C81" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>j3</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="C82" t="n">
+        <v>4.409</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>j4</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2.888</v>
+      </c>
+      <c r="C83" t="n">
+        <v>4.591</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>j5</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="C84" t="n">
+        <v>4.579</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>j6</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="C85" t="n">
+        <v>4.641</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>j1</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="C86" t="n">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>j2</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>2.651</v>
+      </c>
+      <c r="C87" t="n">
+        <v>3.702</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>j3</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="C88" t="n">
+        <v>4.393</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>j4</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>2.877</v>
+      </c>
+      <c r="C89" t="n">
+        <v>4.582</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>j5</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>2.651</v>
+      </c>
+      <c r="C90" t="n">
+        <v>4.593</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>j6</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>3.064</v>
+      </c>
+      <c r="C91" t="n">
+        <v>4.662</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>j1</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>2.592</v>
+      </c>
+      <c r="C92" t="n">
+        <v>4.589</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>j2</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>2.663</v>
+      </c>
+      <c r="C93" t="n">
+        <v>3.707</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>j3</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="C94" t="n">
+        <v>4.425</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>j4</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>2.872</v>
+      </c>
+      <c r="C95" t="n">
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>j5</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>2.672</v>
+      </c>
+      <c r="C96" t="n">
+        <v>4.581</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>j6</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>3.036</v>
+      </c>
+      <c r="C97" t="n">
+        <v>4.657</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>j1</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>2.626</v>
+      </c>
+      <c r="C98" t="n">
+        <v>4.583</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>j2</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="C99" t="n">
+        <v>3.748</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>j3</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>2.213</v>
+      </c>
+      <c r="C100" t="n">
+        <v>4.427</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>j4</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>2.881</v>
+      </c>
+      <c r="C101" t="n">
+        <v>4.592</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>j5</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C102" t="n">
+        <v>4.594</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>j6</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>3.054</v>
+      </c>
+      <c r="C103" t="n">
+        <v>4.66</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>j1</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2.554</v>
+      </c>
+      <c r="C104" t="n">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>j2</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>2.656</v>
+      </c>
+      <c r="C105" t="n">
+        <v>3.694</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>j3</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>3.507</v>
+      </c>
+      <c r="C106" t="n">
+        <v>4.412</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>j4</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>2.873</v>
+      </c>
+      <c r="C107" t="n">
+        <v>4.655</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>j5</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>2.739</v>
+      </c>
+      <c r="C108" t="n">
+        <v>4.594</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>j6</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>3.054</v>
+      </c>
+      <c r="C109" t="n">
+        <v>4.649</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
